--- a/doc/4、日常管理/DFDL33-SH8619版本发布记录/DFDL33-SH8619_BootV1.0.0.1_AppV1.0.0.6/DFDL33-SH8619 协议转换单元软件版本对照表.xlsx
+++ b/doc/4、日常管理/DFDL33-SH8619版本发布记录/DFDL33-SH8619_BootV1.0.0.1_AppV1.0.0.6/DFDL33-SH8619 协议转换单元软件版本对照表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\SVN\DFDL33-SH8619\doc\4、日常管理\DFDL33-SH8619版本发布记录\DFDL33-SH8619_BootV1.0.0.1_AppV1.0.0.6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF2FE8E-207C-4F35-88AA-FA47AA5915AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7643F4C5-B6B0-45C7-89A0-B680DA020AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2775" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -261,20 +261,20 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>V1.0.0.109</t>
+    <t>V1.0.0.110</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>影响范围：
 1、开关机、有功数值、无功数值、功率因素、有功百分比、无功百分比全控逻辑
-2、华为1逆变器识别</t>
+2、华为1、2逆变器识别</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、调整时段控全控逻辑，遍历时段控，有效则保存，无效则跳过；
 2、调整全控返回报文，全控正常则返回正常应答报文，存在一个异常，则返回错误错误应答，错误码01；
 3、调整开关机全控逻辑，支持FF不进行控制；
-4、调整华为逆变器特征寄存器地址和范围判断。</t>
+4、调整华为逆变器特征寄存器地址和范围判断，目前华为2会被识别成华为1，需手动修改档案。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
